--- a/ig/ch-term/ValueSet-ch-vacd-swissmedic-immunoglobulin-vs.xlsx
+++ b/ig/ch-term/ValueSet-ch-vacd-swissmedic-immunoglobulin-vs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="106">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.3.0</t>
+    <t>3.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-15T10:47:47+00:00</t>
+    <t>2026-06-10T10:00:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -130,12 +130,6 @@
   </si>
   <si>
     <t>Beyfortus 50 mg/0.5 ml, solution injectable en seringue préremplie</t>
-  </si>
-  <si>
-    <t>65745-01</t>
-  </si>
-  <si>
-    <t>Antivipmyn</t>
   </si>
   <si>
     <t>68222-01</t>
@@ -610,7 +604,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B40"/>
+  <dimension ref="A1:B39"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -918,23 +912,15 @@
         <v>103</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B39" t="s" s="2">
         <v>105</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="B40" t="s" s="2">
-        <v>107</v>
       </c>
     </row>
   </sheetData>
